--- a/red_book/excel/笔记列表明细表-20260821.xlsx
+++ b/red_book/excel/笔记列表明细表-20260821.xlsx
@@ -95,7 +95,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="25.0" customWidth="true"/>
@@ -250,12 +250,12 @@
     <row r="3" customHeight="true" ht="20.0">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>不用酸奶机，0工具也能快速简单做酸奶</t>
+          <t>照着这份居家维护清单，慢慢把你的家养顺</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026年08月21日11时53分06秒</t>
+          <t>2026年08月19日12时53分37秒</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -264,31 +264,31 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.0</v>
+        <v>1266.0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>47.0</v>
+        <v>120.0</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.0</v>
+        <v>0.095</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.0</v>
+        <v>33.0</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0.0</v>
@@ -297,12 +297,12 @@
     <row r="4" customHeight="true" ht="20.0">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>照着这份居家维护清单，慢慢把你的家养顺</t>
+          <t>台面、玻璃胶发霉？涂一层这个，焕然一新</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026年08月19日12时53分37秒</t>
+          <t>2026年08月17日11时38分46秒</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -311,31 +311,31 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1266.0</v>
+        <v>1591.0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>124.0</v>
+        <v>103.0</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.095</v>
+        <v>0.065</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>33.0</v>
+        <v>22.0</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0.0</v>
@@ -344,12 +344,12 @@
     <row r="5" customHeight="true" ht="20.0">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>台面、玻璃胶发霉？涂一层这个，焕然一新</t>
+          <t>降低公积金比例，把差额发工资，都是套路！</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026年08月17日11时38分46秒</t>
+          <t>2026年08月14日19时56分36秒</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -358,13 +358,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1591.0</v>
+        <v>281.0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>107.0</v>
+        <v>14.0</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.065</v>
+        <v>0.05</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0.0</v>
@@ -373,7 +373,7 @@
         <v>0.0</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0.0</v>
@@ -382,7 +382,7 @@
         <v>0.0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>22.0</v>
+        <v>37.0</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>0.0</v>
@@ -391,12 +391,12 @@
     <row r="6" customHeight="true" ht="20.0">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>降低公积金比例，把差额发工资，都是套路！</t>
+          <t>加装内存条保密级教程，零基础宝妈自己搞定</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026年08月14日19时56分36秒</t>
+          <t>2026年08月13日13时08分19秒</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -405,31 +405,31 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>281.0</v>
+        <v>6809.0</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>14.0</v>
+        <v>973.0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.0</v>
+        <v>30.0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>37.0</v>
+        <v>41.0</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>0.0</v>
@@ -438,12 +438,12 @@
     <row r="7" customHeight="true" ht="20.0">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>加装内存条保密级教程，零基础宝妈自己搞定</t>
+          <t>我理解汪峰，但我害怕成为那700人</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026年08月13日13时08分19秒</t>
+          <t>2026年08月11日13时33分21秒</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -452,31 +452,31 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6809.0</v>
+        <v>436.0</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1060.0</v>
+        <v>28.0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.14</v>
+        <v>0.067</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>31.0</v>
+        <v>1.0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>41.0</v>
+        <v>20.0</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>0.0</v>
@@ -485,12 +485,12 @@
     <row r="8" customHeight="true" ht="20.0">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>我理解汪峰，但我害怕成为那700人</t>
+          <t>电子玩具充不进电？别扔，换块电池就行</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026年08月11日13时33分21秒</t>
+          <t>2026年08月10日12时51分36秒</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -499,22 +499,22 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>436.0</v>
+        <v>1207.0</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>28.0</v>
+        <v>88.0</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.067</v>
+        <v>0.07</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>0.0</v>
@@ -523,7 +523,7 @@
         <v>0.0</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>20.0</v>
+        <v>24.0</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>0.0</v>
@@ -532,12 +532,12 @@
     <row r="9" customHeight="true" ht="20.0">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>电子玩具充不进电？别扔，换块电池就行</t>
+          <t>门把手松动？别叫师傅！4种故障轻松搞定</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026年08月10日12时51分36秒</t>
+          <t>2026年08月08日13时05分14秒</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -546,31 +546,31 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1207.0</v>
+        <v>12745.0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>89.0</v>
+        <v>1299.0</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.07</v>
+        <v>0.101</v>
       </c>
       <c r="G9" s="2" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="H9" s="2" t="n">
         <v>5.0</v>
       </c>
-      <c r="H9" s="2" t="n">
-        <v>4.0</v>
-      </c>
       <c r="I9" s="2" t="n">
-        <v>2.0</v>
+        <v>57.0</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>24.0</v>
+        <v>22.0</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>0.0</v>
@@ -579,12 +579,12 @@
     <row r="10" customHeight="true" ht="20.0">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>门把手松动？别叫师傅！4种故障轻松搞定</t>
+          <t>二胎宝妈如何0元修好点读笔</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026年08月08日13时05分14秒</t>
+          <t>2026年08月07日12时19分17秒</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -593,31 +593,31 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>12745.0</v>
+        <v>974.0</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1333.0</v>
+        <v>72.0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.101</v>
+        <v>0.077</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>35.0</v>
+        <v>2.0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>57.0</v>
+        <v>2.0</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>22.0</v>
+        <v>16.0</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>0.0</v>
@@ -626,12 +626,12 @@
     <row r="11" customHeight="true" ht="20.0">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>二胎宝妈如何0元修好点读笔</t>
+          <t>11年老员工被打0绩效，这次我决不妥协</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2026年08月07日12时19分17秒</t>
+          <t>2026年08月05日13时22分38秒</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -640,31 +640,31 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>974.0</v>
+        <v>131.0</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>72.0</v>
+        <v>15.0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.077</v>
+        <v>0.122</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>2.0</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>16.0</v>
+        <v>21.0</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>0.0</v>
@@ -673,12 +673,12 @@
     <row r="12" customHeight="true" ht="20.0">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>11年老员工被打0绩效，这次我决不妥协</t>
+          <t>一叠尘封契约，揭开神医的真相</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026年08月05日13时22分38秒</t>
+          <t>2026年08月01日13时17分13秒</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -687,31 +687,31 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>131.0</v>
+        <v>392.0</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.122</v>
+        <v>0.028</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>21.0</v>
+        <v>48.0</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>0.0</v>
@@ -720,12 +720,12 @@
     <row r="13" customHeight="true" ht="20.0">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>一叠尘封契约，揭开神医的真相</t>
+          <t>困住你的不该是你的来时路|沉没成本</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>2026年08月01日13时17分13秒</t>
+          <t>2026年07月25日19时51分40秒</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -734,13 +734,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>392.0</v>
+        <v>581.0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>12.0</v>
+        <v>17.0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.028</v>
+        <v>0.029</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>1.0</v>
@@ -749,16 +749,16 @@
         <v>0.0</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>0.0</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>48.0</v>
+        <v>8.0</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>0.0</v>
@@ -767,12 +767,12 @@
     <row r="14" customHeight="true" ht="20.0">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>困住你的不该是你的来时路|沉没成本</t>
+          <t>收藏点赞破10！小小记录一下</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026年07月25日19时51分40秒</t>
+          <t>2026年07月22日13时19分13秒</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>581.0</v>
+        <v>297.0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>17.0</v>
+        <v>2.0</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.029</v>
+        <v>0.01</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>0.0</v>
@@ -805,7 +805,7 @@
         <v>0.0</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>8.0</v>
+        <v>14.0</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0.0</v>
@@ -814,12 +814,12 @@
     <row r="15" customHeight="true" ht="20.0">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>收藏点赞破10！小小记录一下</t>
+          <t>跳出内耗：抓住自己的初始优势｜马太效应</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2026年07月22日13时19分13秒</t>
+          <t>2026年07月21日12时39分38秒</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -828,80 +828,33 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>297.0</v>
+        <v>1758.0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2.0</v>
+        <v>219.0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.01</v>
+        <v>0.126</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="16" customHeight="true" ht="20.0">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>跳出内耗：抓住自己的初始优势｜马太效应</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>2026年07月21日12时39分38秒</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>图文</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>1758.0</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>219.0</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>14.0</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>13.0</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="M16" s="2" t="n">
         <v>0.0</v>
       </c>
     </row>
